--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1246,7 +1246,7 @@
     <t>outboundRelationship[typeCode=COMP].target</t>
   </si>
   <si>
-    <t>++: reference from null (#null)</t>
+    <t>++: reference</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA CHEM, HEM, TOX, RIA, SER, etc. (file 63.04) to FHIR DiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to LabObservationDiagnosticReport</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$43</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Chem, hem, tox, ria, ser {DiagnosticReport}</t>
+    <t>Lab Observation: Chem, hem, tox, ria, ser DiagnosticReport</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to LabObservationDiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/LabObservationDiagnosticReport</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -818,74 +818,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-2:1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB {null}</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>DiagnosticReport.category:LaboratorySlice</t>
@@ -966,30 +898,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -1724,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR47"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -1766,10 +1674,8 @@
     <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="159.9140625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="50.07421875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="165.01953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="50.07421875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1899,12 +1805,6 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
-      <c r="AQ1" t="s" s="1">
-        <v>77</v>
-      </c>
-      <c r="AR1" t="s" s="1">
-        <v>78</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2025,12 +1925,6 @@
       <c r="AP2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR2" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2151,12 +2045,6 @@
       <c r="AP3" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR3" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2275,12 +2163,6 @@
       <c r="AP4" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR4" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2401,12 +2283,6 @@
       <c r="AP5" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR5" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -2527,12 +2403,6 @@
       <c r="AP6" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR6" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -2653,12 +2523,6 @@
       <c r="AP7" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR7" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -2779,12 +2643,6 @@
       <c r="AP8" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR8" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -2905,12 +2763,6 @@
       <c r="AP9" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR9" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3033,12 +2885,6 @@
       <c r="AP10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR10" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3161,12 +3007,6 @@
       <c r="AP11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR11" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3285,12 +3125,6 @@
       <c r="AP12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR12" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -3411,12 +3245,6 @@
       <c r="AP13" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR13" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -3539,12 +3367,6 @@
       <c r="AP14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR14" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -3667,12 +3489,6 @@
       <c r="AP15" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR15" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -3795,12 +3611,6 @@
       <c r="AP16" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -3821,7 +3631,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
@@ -3919,12 +3729,6 @@
         <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AR17" t="s" s="2">
         <v>82</v>
       </c>
     </row>
@@ -4045,12 +3849,6 @@
       <c r="AP18" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR18" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4171,12 +3969,6 @@
       <c r="AP19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR19" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4299,12 +4091,6 @@
       <c r="AP20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -4423,12 +4209,6 @@
       <c r="AP21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ21" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -4547,50 +4327,48 @@
       <c r="AP22" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AQ22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4600,7 +4378,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4615,13 +4393,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4639,83 +4417,77 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR23" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4741,89 +4513,83 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR24" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4832,19 +4598,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4893,55 +4657,49 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>267</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AR25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4960,19 +4718,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5021,7 +4779,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5036,46 +4794,38 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AR26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5090,18 +4840,20 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5110,7 +4862,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5125,83 +4877,77 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5216,18 +4962,20 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>308</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5251,13 +4999,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5275,59 +5023,53 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5342,17 +5084,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5401,7 +5145,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5410,56 +5154,50 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5468,19 +5206,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5529,13 +5267,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5544,50 +5282,44 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR30" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5596,19 +5328,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5645,98 +5377,92 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR31" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5785,62 +5511,56 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>92</v>
@@ -5849,22 +5569,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5913,16 +5633,16 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
@@ -5931,37 +5651,31 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5971,29 +5685,27 @@
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6041,7 +5753,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6056,40 +5768,34 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AR34" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6108,19 +5814,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6169,7 +5873,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6184,36 +5888,30 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR35" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6224,7 +5922,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6236,20 +5934,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>368</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6297,28 +5991,28 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6327,12 +6021,6 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR36" t="s" s="2">
         <v>82</v>
       </c>
     </row>
@@ -6345,7 +6033,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>375</v>
+        <v>136</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6355,7 +6043,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6364,20 +6052,18 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>138</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6425,7 +6111,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6437,43 +6123,37 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>164</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AR37" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6486,24 +6166,26 @@
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>385</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6551,7 +6233,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6563,7 +6245,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6572,7 +6254,7 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>389</v>
+        <v>134</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6581,32 +6263,26 @@
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR38" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6615,20 +6291,22 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>392</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6677,13 +6355,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6695,10 +6373,10 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6707,21 +6385,15 @@
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR39" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6729,7 +6401,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -6741,16 +6413,16 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>387</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>388</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
+        <v>389</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6801,10 +6473,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -6813,7 +6485,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6822,7 +6494,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>164</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6831,32 +6503,26 @@
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR40" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>392</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6868,18 +6534,18 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>393</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6927,28 +6593,28 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>391</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>164</v>
+        <v>397</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6957,25 +6623,19 @@
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR41" t="s" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6988,26 +6648,22 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7031,13 +6687,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7055,7 +6711,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7067,16 +6723,16 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>134</v>
+        <v>403</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7085,12 +6741,6 @@
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
@@ -7110,7 +6760,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7122,19 +6772,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>405</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7189,7 +6839,7 @@
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7201,10 +6851,10 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -7213,519 +6863,11 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR47">
+  <autoFilter ref="A1:AP43">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7735,7 +6877,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI42">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -746,6 +746,9 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>1687: reference from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.04-.35 &gt; 63.07-3)</t>
   </si>
   <si>
     <t>DiagnosticReport.status</t>
@@ -1049,7 +1052,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole)
 </t>
   </si>
   <si>
@@ -1077,7 +1080,7 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>1433: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (#63.04-.04)</t>
+    <t>1683: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSIONING INSTITUTION (#63.04-.112)</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -1132,7 +1135,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationChemhemtoxriaserObservation)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab)
 </t>
   </si>
   <si>
@@ -1152,9 +1155,6 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>++: reference</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>
@@ -1645,7 +1645,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.3515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3989,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
@@ -4086,7 +4086,7 @@
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4123,14 +4123,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4177,7 +4177,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4186,25 +4186,25 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4212,14 +4212,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4241,13 +4241,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4273,19 +4273,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4295,7 +4295,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4313,13 +4313,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4330,16 +4330,16 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4361,13 +4361,13 @@
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4378,7 +4378,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4393,13 +4393,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4417,7 +4417,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4435,13 +4435,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4452,14 +4452,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4481,13 +4481,13 @@
         <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4516,10 +4516,10 @@
         <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4537,7 +4537,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -4552,16 +4552,16 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4572,14 +4572,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4598,17 +4598,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4657,7 +4657,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4672,16 +4672,16 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -4692,14 +4692,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4718,19 +4718,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4779,7 +4779,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4794,16 +4794,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4814,14 +4814,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4840,19 +4840,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4889,7 +4889,7 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -4899,7 +4899,7 @@
         <v>169</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4908,22 +4908,22 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -4934,16 +4934,16 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4962,19 +4962,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5023,7 +5023,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5032,40 +5032,40 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5084,19 +5084,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5145,7 +5145,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5154,7 +5154,7 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
@@ -5163,31 +5163,31 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5206,19 +5206,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5267,7 +5267,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5282,19 +5282,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5302,14 +5302,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5328,19 +5328,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5389,7 +5389,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5404,16 +5404,16 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5450,19 +5450,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5511,7 +5511,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5529,10 +5529,10 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5546,14 +5546,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5572,19 +5572,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5651,16 +5651,16 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5894,7 +5894,7 @@
         <v>372</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6687,7 +6687,7 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y42" t="s" s="2">
         <v>401</v>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,7 +520,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -935,7 +935,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="426">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -952,6 +955,27 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Micro.BacteriologyReports.LRDFN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN
+Pathology.Autopsy.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1663,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP49"/>
+  <dimension ref="A1:AQ49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.1328125" customWidth="true" bestFit="true"/>
@@ -1703,10 +1727,11 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="42.265625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1836,6 +1861,9 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1846,106 +1874,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>88</v>
@@ -1954,1080 +1982,1107 @@
         <v>89</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>82</v>
+        <v>127</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>156</v>
@@ -3037,119 +3092,122 @@
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
+        <v>159</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>168</v>
@@ -3158,116 +3216,119 @@
         <v>169</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>178</v>
@@ -3277,839 +3338,860 @@
       </c>
       <c r="AP13" t="s" s="2">
         <v>180</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
+        <v>181</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AE14" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>194</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH17" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>224</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>194</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>238</v>
@@ -4119,3508 +4201,3598 @@
       </c>
       <c r="AP20" t="s" s="2">
         <v>240</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>241</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH22" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH25" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>256</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>263</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>271</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>279</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>288</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>224</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>316</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>328</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF37" t="s" s="2">
+      <c r="AI37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>348</v>
+      <c r="AQ37" t="s" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
+      <c r="AI48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP49">
+  <autoFilter ref="A1:AQ49">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="424">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -955,27 +952,6 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Micro.BacteriologyReports.LRDFN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN
-Pathology.Autopsy.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1687,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ49"/>
+  <dimension ref="A1:AP49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.1328125" customWidth="true" bestFit="true"/>
@@ -1727,11 +1703,10 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.265625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1861,9 +1836,6 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
-      <c r="AQ1" t="s" s="1">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1874,106 +1846,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="M2" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="N2" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>88</v>
@@ -1982,1107 +1954,1080 @@
         <v>89</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AQ2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="AG7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AQ7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AG8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP8" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>143</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>147</v>
-      </c>
       <c r="P10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="P11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>156</v>
@@ -3092,122 +3037,119 @@
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H12" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="P12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH12" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>168</v>
@@ -3216,119 +3158,116 @@
         <v>169</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AQ12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G13" t="s" s="2">
+      <c r="I13" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI13" t="s" s="2">
+      <c r="AJ13" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>178</v>
@@ -3338,860 +3277,839 @@
       </c>
       <c r="AP13" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>181</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP15" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="P17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="P18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>224</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="D19" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H19" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G19" t="s" s="2">
+      <c r="I19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K19" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="T19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="AL19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G20" t="s" s="2">
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AA20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>238</v>
@@ -4201,3598 +4119,3508 @@
       </c>
       <c r="AP20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>241</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP21" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AC22" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AD22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AD22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O23" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="P23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP24" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AC25" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="O26" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="P26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>256</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>263</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H28" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>271</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H29" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AL29" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>279</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="O30" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="P30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>288</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H31" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="P31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>83</v>
+        <v>223</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>224</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G32" t="s" s="2">
+      <c r="I32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K33" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="P33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="P34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>328</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="P35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H36" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="P36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH36" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="O37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH37" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AP37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G38" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="P38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH38" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="P39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP42" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M43" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="P45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K46" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="AP48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="P49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ49">
+  <autoFilter ref="A1:AP49">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="426">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -952,6 +955,9 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
+    <t>demographics.lrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1663,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP49"/>
+  <dimension ref="A1:AQ49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.1328125" customWidth="true" bestFit="true"/>
@@ -1703,10 +1709,11 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1836,6 +1843,9 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1846,106 +1856,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>88</v>
@@ -1954,1080 +1964,1107 @@
         <v>89</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>82</v>
+        <v>127</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>156</v>
@@ -3037,119 +3074,122 @@
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
+        <v>159</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>168</v>
@@ -3158,116 +3198,119 @@
         <v>169</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>178</v>
@@ -3277,839 +3320,860 @@
       </c>
       <c r="AP13" t="s" s="2">
         <v>180</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
+        <v>181</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AE14" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>194</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH17" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>224</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>194</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>238</v>
@@ -4119,3508 +4183,3598 @@
       </c>
       <c r="AP20" t="s" s="2">
         <v>240</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>241</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH22" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH25" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>256</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>263</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>271</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>279</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>288</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>224</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>316</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>328</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF37" t="s" s="2">
+      <c r="AI37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>348</v>
+      <c r="AQ37" t="s" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
+      <c r="AI48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="S49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP49">
+  <autoFilter ref="A1:AQ49">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -957,7 +957,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1710,7 +1710,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -957,8 +957,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -957,7 +957,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (63.04) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (63.04) to us-core-diagnosticreport-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -571,6 +571,9 @@
   <si>
     <t>us-core-8
 us-core-9</t>
+  </si>
+  <si>
+    <t>2050: target not supported</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1030,6 +1033,10 @@
     <t>Need to know where in the patient history to file/present this report.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-8
 </t>
   </si>
@@ -1046,6 +1053,19 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>DiagnosticReport.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>2051: target not supported</t>
+  </si>
+  <si>
     <t>DiagnosticReport.issued</t>
   </si>
   <si>
@@ -1073,6 +1093,9 @@
 </t>
   </si>
   <si>
+    <t>2052: target not supported</t>
+  </si>
+  <si>
     <t>OBR-22</t>
   </si>
   <si>
@@ -1103,6 +1126,9 @@
   </si>
   <si>
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
+  </si>
+  <si>
+    <t>2053: target not supported</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1669,12 +1695,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ49"/>
+  <dimension ref="A1:AQ50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.1328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.34765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3304,7 +3330,7 @@
         <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
@@ -3313,28 +3339,28 @@
         <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3353,16 +3379,16 @@
         <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3388,29 +3414,29 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3437,21 +3463,21 @@
         <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3474,13 +3500,13 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3531,7 +3557,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3561,7 +3587,7 @@
         <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>83</v>
@@ -3569,10 +3595,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3601,7 +3627,7 @@
         <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>141</v>
@@ -3642,19 +3668,19 @@
         <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3684,7 +3710,7 @@
         <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>83</v>
@@ -3692,10 +3718,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3718,19 +3744,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3779,7 +3805,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3806,10 +3832,10 @@
         <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -3817,10 +3843,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3843,19 +3869,19 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
@@ -3904,7 +3930,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3919,10 +3945,10 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>83</v>
@@ -3931,10 +3957,10 @@
         <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>83</v>
@@ -3942,16 +3968,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3970,16 +3996,16 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3990,7 +4016,7 @@
         <v>83</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>83</v>
@@ -4005,13 +4031,13 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
@@ -4029,7 +4055,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4044,7 +4070,7 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
@@ -4056,25 +4082,25 @@
         <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4093,16 +4119,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4128,13 +4154,13 @@
         <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>83</v>
@@ -4152,7 +4178,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>92</v>
@@ -4176,24 +4202,24 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4216,13 +4242,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4273,7 +4299,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4303,7 +4329,7 @@
         <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4311,10 +4337,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4343,7 +4369,7 @@
         <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>141</v>
@@ -4384,19 +4410,19 @@
         <v>83</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4426,7 +4452,7 @@
         <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -4434,10 +4460,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4460,19 +4486,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4521,7 +4547,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4536,10 +4562,10 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>83</v>
@@ -4548,10 +4574,10 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4559,10 +4585,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4585,13 +4611,13 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4642,7 +4668,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4672,7 +4698,7 @@
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -4680,10 +4706,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4712,7 +4738,7 @@
         <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>141</v>
@@ -4753,19 +4779,19 @@
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4795,7 +4821,7 @@
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>83</v>
@@ -4803,10 +4829,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4832,16 +4858,16 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4851,7 +4877,7 @@
         <v>83</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>83</v>
@@ -4890,7 +4916,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4905,7 +4931,7 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>83</v>
@@ -4917,10 +4943,10 @@
         <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -4928,10 +4954,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4954,16 +4980,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5013,7 +5039,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5040,10 +5066,10 @@
         <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5051,10 +5077,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5080,14 +5106,14 @@
         <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5136,7 +5162,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5151,10 +5177,10 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
@@ -5163,10 +5189,10 @@
         <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5174,10 +5200,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5200,17 +5226,17 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5259,7 +5285,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5274,10 +5300,10 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
@@ -5286,10 +5312,10 @@
         <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5297,10 +5323,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5323,19 +5349,19 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5384,7 +5410,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5411,10 +5437,10 @@
         <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5422,10 +5448,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5448,19 +5474,19 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5509,7 +5535,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5524,10 +5550,10 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>83</v>
@@ -5536,10 +5562,10 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5547,14 +5573,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5573,17 +5599,17 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5632,7 +5658,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5647,37 +5673,37 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5696,19 +5722,19 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5757,7 +5783,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5781,28 +5807,28 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5821,19 +5847,19 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -5870,19 +5896,17 @@
         <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5891,7 +5915,7 @@
         <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>104</v>
@@ -5906,28 +5930,30 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5946,19 +5972,19 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6007,7 +6033,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6016,13 +6042,13 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>83</v>
+        <v>334</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
@@ -6031,35 +6057,35 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>93</v>
@@ -6071,19 +6097,19 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6132,22 +6158,22 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>342</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -6156,28 +6182,28 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6187,7 +6213,7 @@
         <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>83</v>
@@ -6196,19 +6222,19 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O37" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6257,7 +6283,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6272,7 +6298,7 @@
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
@@ -6281,28 +6307,28 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AP37" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AQ37" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6318,22 +6344,22 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6382,7 +6408,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6406,28 +6432,28 @@
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6437,7 +6463,7 @@
         <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -6507,7 +6533,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6522,22 +6548,22 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>305</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6545,14 +6571,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6562,7 +6588,7 @@
         <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
@@ -6571,18 +6597,20 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6630,7 +6658,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6645,7 +6673,7 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
@@ -6657,10 +6685,10 @@
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -6668,14 +6696,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6691,21 +6719,21 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
         <v>386</v>
       </c>
+      <c r="N41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6753,7 +6781,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6780,10 +6808,10 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -6791,21 +6819,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6814,19 +6842,21 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>197</v>
+        <v>391</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>198</v>
+        <v>392</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>199</v>
+        <v>393</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -6874,19 +6904,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>200</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6901,10 +6931,10 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>201</v>
+        <v>382</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -6912,21 +6942,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -6938,17 +6968,15 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -6997,19 +7025,19 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7027,7 +7055,7 @@
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
@@ -7035,14 +7063,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>391</v>
+        <v>137</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7055,26 +7083,24 @@
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>139</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>204</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7122,7 +7148,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>207</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7152,7 +7178,7 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7160,45 +7186,45 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>398</v>
+        <v>141</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>399</v>
+        <v>147</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7247,19 +7273,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7277,7 +7303,7 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -7285,10 +7311,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7296,7 +7322,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>92</v>
@@ -7308,19 +7334,23 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>402</v>
+        <v>198</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7368,10 +7398,10 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>92</v>
@@ -7398,7 +7428,7 @@
         <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -7406,18 +7436,18 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>92</v>
@@ -7429,21 +7459,19 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>197</v>
+        <v>410</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>410</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7491,10 +7519,10 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>92</v>
@@ -7518,10 +7546,10 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -7529,21 +7557,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7555,16 +7583,18 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7588,13 +7618,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>416</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7612,13 +7642,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7639,10 +7669,10 @@
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -7650,10 +7680,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7676,20 +7706,16 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>420</v>
+        <v>185</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="O49" t="s" s="2">
-        <v>424</v>
-      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7713,13 +7739,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7737,7 +7763,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7764,17 +7790,142 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ49" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ49">
+  <autoFilter ref="A1:AQ50">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7784,7 +7935,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -539,7 +539,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>1687: reference from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.04-.35 &gt; 63.07-3)</t>
+    <t>1687: reference based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.04-.35 &gt; 63.07-3)</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -714,7 +714,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
@@ -789,7 +789,7 @@
     <t>DiagnosticReport.code.coding</t>
   </si>
   <si>
-    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+    <t>1420: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding.id</t>
@@ -864,7 +864,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
+    <t>1420-1: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -888,7 +888,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
+    <t>1420-3: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -928,7 +928,7 @@
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
-    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+    <t>1661: source value based on LABORATORY TEST - NAME (60-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.LabChemTestName</t>
@@ -954,7 +954,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1211,7 +1211,7 @@
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
   </si>
   <si>
-    <t>1437: reference from See mapping for Lab Observation</t>
+    <t>1437: reference based on See mapping for Lab Observation</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -1733,7 +1733,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="167.57421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1195,7 +1195,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationObservation)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationChemhemtoxriaserObservation)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -954,13 +951,11 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
-  </si>
-  <si>
-    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+locdr-46-1421:If PATIENT - LABORATORY REFERENCE (2-63) == LAB DATA – LRDFN (63-.01) then reference /Patient based on (2-) {true}</t>
+  </si>
+  <si>
+    <t>1421: reference based on PATIENT - (2-) if PATIENT - LABORATORY REFERENCE (2-63) == LAB DATA – LRDFN (63-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1695,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ50"/>
+  <dimension ref="A1:AP50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -1734,12 +1729,11 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="167.57421875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1869,9 +1863,6 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
-      <c r="AQ1" t="s" s="1">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1882,106 +1873,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="M2" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="N2" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>88</v>
@@ -1990,1107 +1981,1080 @@
         <v>89</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AQ2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="AG7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AQ7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AG8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP8" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ8" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>143</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ9" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>147</v>
-      </c>
       <c r="P10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ10" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="P11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>156</v>
@@ -3100,122 +3064,119 @@
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H12" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="P12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH12" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>168</v>
@@ -3224,119 +3185,116 @@
         <v>169</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AQ12" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G13" t="s" s="2">
+      <c r="I13" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI13" t="s" s="2">
+      <c r="AJ13" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>179</v>
@@ -3346,860 +3304,839 @@
       </c>
       <c r="AP13" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>182</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>194</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="P17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>215</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>221</v>
-      </c>
       <c r="P18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>225</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="D19" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H19" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G19" t="s" s="2">
+      <c r="I19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K19" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="T19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AL19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>194</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G20" t="s" s="2">
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AA20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>239</v>
@@ -4209,3723 +4146,3630 @@
       </c>
       <c r="AP20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC22" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AD22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AD22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="O23" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="P23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>215</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP24" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AC25" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="P26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>257</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>264</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H28" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>272</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H29" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AL29" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>280</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="O30" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="P30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>289</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H31" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>221</v>
-      </c>
       <c r="P31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>225</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G32" t="s" s="2">
+      <c r="I32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>300</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="P33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>312</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="P34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="P35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H36" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="P36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N37" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="P37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH37" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G38" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="O38" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH38" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AP38" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="P39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>372</v>
+        <v>303</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="P40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AP40" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH42" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP43" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M44" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH45" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="P46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G47" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K47" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AP49" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G50" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="P50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AH50" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ50">
+  <autoFilter ref="A1:AP50">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
